--- a/zy72088/ml_threshold_calibrator/output/demo_conflicts_latest.xlsx
+++ b/zy72088/ml_threshold_calibrator/output/demo_conflicts_latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>metric_name</t>
   </si>
@@ -40,22 +40,13 @@
     <t>DAU日活用户</t>
   </si>
   <si>
-    <t>客单价</t>
-  </si>
-  <si>
     <t>阿乔202402手动调过：春节期间活动拉高，恢复正常后回落</t>
   </si>
   <si>
-    <t>2023年底校准：大促后均值稳定在140-160区间</t>
-  </si>
-  <si>
     <t>请核对两边数据来源，确认哪个是正确口径后手动调整</t>
   </si>
   <si>
     <t>{'参数表来源': '阈值=100000.0, 备注=阿乔202402手动调过：春节期间活动拉高，恢复正常后回落', '导入数据来源': '阈值=95000.0'}</t>
-  </si>
-  <si>
-    <t>{'参数表来源': '阈值=150.0, 备注=2023年底校准：大促后均值稳定在140-160区间', '导入数据来源': '阈值=180.0'}</t>
   </si>
 </sst>
 </file>
@@ -413,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -453,36 +444,13 @@
         <v>5000</v>
       </c>
       <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
       <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>150</v>
-      </c>
-      <c r="C3">
-        <v>180</v>
-      </c>
-      <c r="D3">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
         <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
